--- a/refs/heads/main/StructureDefinition-DDCCCoreDataSet.VS.PoV.xlsx
+++ b/refs/heads/main/StructureDefinition-DDCCCoreDataSet.VS.PoV.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-14T21:40:28+00:00</t>
+    <t>2023-12-14T13:07:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-DDCCCoreDataSet.VS.PoV.xlsx
+++ b/refs/heads/main/StructureDefinition-DDCCCoreDataSet.VS.PoV.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-14T13:07:01+00:00</t>
+    <t>2023-12-14T13:50:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-DDCCCoreDataSet.VS.PoV.xlsx
+++ b/refs/heads/main/StructureDefinition-DDCCCoreDataSet.VS.PoV.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-14T13:50:56+00:00</t>
+    <t>2023-12-15T03:05:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-DDCCCoreDataSet.VS.PoV.xlsx
+++ b/refs/heads/main/StructureDefinition-DDCCCoreDataSet.VS.PoV.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-15T03:05:37+00:00</t>
+    <t>2024-01-19T16:18:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-DDCCCoreDataSet.VS.PoV.xlsx
+++ b/refs/heads/main/StructureDefinition-DDCCCoreDataSet.VS.PoV.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1376" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1339" uniqueCount="194">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-19T16:18:21+00:00</t>
+    <t>2024-04-24T00:11:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -222,9 +222,6 @@
     <t>Element.id</t>
   </si>
   <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>DDCCCoreDataSet.certificate.extension</t>
   </si>
   <si>
@@ -282,9 +279,6 @@
     <t>BackboneElement.modifierExtension</t>
   </si>
   <si>
-    <t>N/A</t>
-  </si>
-  <si>
     <t>DDCCCoreDataSet.certificate.issuer</t>
   </si>
   <si>
@@ -383,9 +377,6 @@
 </t>
   </si>
   <si>
-    <t>./low</t>
-  </si>
-  <si>
     <t>DDCCCoreDataSet.certificate.period.end</t>
   </si>
   <si>
@@ -402,9 +393,6 @@
   </si>
   <si>
     <t>Period.end</t>
-  </si>
-  <si>
-    <t>./high</t>
   </si>
   <si>
     <t>DDCCCoreDataSet.vaccination</t>
@@ -929,7 +917,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO37"/>
+  <dimension ref="A1:AN37"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="46.4140625" customWidth="true" bestFit="true"/>
@@ -966,11 +954,10 @@
     <col min="34" max="34" width="2.2109375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" hidden="true" width="8.0" customWidth="false"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="6.2421875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="98.68359375" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="48.0234375" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="27.9296875" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="17.52734375" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="98.68359375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="48.0234375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="27.9296875" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="17.52734375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1084,9 +1071,6 @@
       <c r="AN1" t="s" s="2">
         <v>37</v>
       </c>
-      <c r="AO1" t="s" s="2">
-        <v>37</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
@@ -1197,9 +1181,6 @@
         <v>37</v>
       </c>
       <c r="AN2" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AO2" t="s" s="2">
         <v>47</v>
       </c>
     </row>
@@ -1312,9 +1293,6 @@
         <v>37</v>
       </c>
       <c r="AN3" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AO3" t="s" s="2">
         <v>52</v>
       </c>
     </row>
@@ -1427,9 +1405,6 @@
         <v>37</v>
       </c>
       <c r="AN4" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AO4" t="s" s="2">
         <v>57</v>
       </c>
     </row>
@@ -1544,9 +1519,6 @@
       <c r="AN5" t="s" s="2">
         <v>37</v>
       </c>
-      <c r="AO5" t="s" s="2">
-        <v>37</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
@@ -1648,7 +1620,7 @@
         <v>37</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>67</v>
+        <v>37</v>
       </c>
       <c r="AL6" t="s" s="2">
         <v>37</v>
@@ -1657,22 +1629,19 @@
         <v>37</v>
       </c>
       <c r="AN6" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AO6" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
@@ -1691,16 +1660,16 @@
         <v>37</v>
       </c>
       <c r="K7" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="L7" t="s" s="2">
         <v>70</v>
       </c>
-      <c r="L7" t="s" s="2">
+      <c r="M7" t="s" s="2">
         <v>71</v>
       </c>
-      <c r="M7" t="s" s="2">
+      <c r="N7" t="s" s="2">
         <v>72</v>
-      </c>
-      <c r="N7" t="s" s="2">
-        <v>73</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -1738,19 +1707,19 @@
         <v>37</v>
       </c>
       <c r="AB7" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC7" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="AC7" t="s" s="2">
+      <c r="AD7" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AE7" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="AD7" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AE7" t="s" s="2">
+      <c r="AF7" t="s" s="2">
         <v>76</v>
-      </c>
-      <c r="AF7" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>38</v>
@@ -1762,10 +1731,10 @@
         <v>37</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AK7" t="s" s="2">
-        <v>67</v>
+        <v>37</v>
       </c>
       <c r="AL7" t="s" s="2">
         <v>37</v>
@@ -1774,22 +1743,19 @@
         <v>37</v>
       </c>
       <c r="AN7" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AO7" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -1808,19 +1774,19 @@
         <v>44</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L8" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="M8" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="M8" t="s" s="2">
+      <c r="N8" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="O8" t="s" s="2">
         <v>82</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="O8" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="P8" t="s" s="2">
         <v>37</v>
@@ -1869,7 +1835,7 @@
         <v>37</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>38</v>
@@ -1881,10 +1847,10 @@
         <v>37</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>85</v>
+        <v>37</v>
       </c>
       <c r="AL8" t="s" s="2">
         <v>37</v>
@@ -1893,18 +1859,15 @@
         <v>37</v>
       </c>
       <c r="AN8" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AO8" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1927,13 +1890,13 @@
         <v>44</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L9" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="M9" t="s" s="2">
         <v>87</v>
-      </c>
-      <c r="L9" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="M9" t="s" s="2">
-        <v>89</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1984,7 +1947,7 @@
         <v>37</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>43</v>
@@ -1999,27 +1962,24 @@
         <v>37</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>90</v>
+        <v>37</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>37</v>
+        <v>89</v>
       </c>
       <c r="AN9" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AO9" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -2045,10 +2005,10 @@
         <v>45</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -2099,7 +2059,7 @@
         <v>37</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>38</v>
@@ -2125,16 +2085,13 @@
       <c r="AN10" t="s" s="2">
         <v>37</v>
       </c>
-      <c r="AO10" t="s" s="2">
-        <v>37</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2160,10 +2117,10 @@
         <v>54</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2214,7 +2171,7 @@
         <v>37</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>43</v>
@@ -2238,18 +2195,15 @@
         <v>37</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AO11" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2275,10 +2229,10 @@
         <v>54</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2329,7 +2283,7 @@
         <v>37</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>38</v>
@@ -2355,16 +2309,13 @@
       <c r="AN12" t="s" s="2">
         <v>37</v>
       </c>
-      <c r="AO12" t="s" s="2">
-        <v>37</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2390,10 +2341,10 @@
         <v>45</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2444,7 +2395,7 @@
         <v>37</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>43</v>
@@ -2468,18 +2419,15 @@
         <v>37</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AO13" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2502,13 +2450,13 @@
         <v>37</v>
       </c>
       <c r="K14" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L14" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="M14" t="s" s="2">
         <v>103</v>
-      </c>
-      <c r="L14" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="M14" t="s" s="2">
-        <v>105</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2559,7 +2507,7 @@
         <v>37</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>38</v>
@@ -2571,7 +2519,7 @@
         <v>37</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>37</v>
@@ -2580,21 +2528,18 @@
         <v>37</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>37</v>
+        <v>105</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AO14" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2689,7 +2634,7 @@
         <v>37</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>67</v>
+        <v>37</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>37</v>
@@ -2698,22 +2643,19 @@
         <v>37</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AO15" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -2732,16 +2674,16 @@
         <v>37</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="L16" t="s" s="2">
         <v>70</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="M16" t="s" s="2">
         <v>71</v>
       </c>
-      <c r="M16" t="s" s="2">
+      <c r="N16" t="s" s="2">
         <v>72</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>73</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -2779,19 +2721,19 @@
         <v>37</v>
       </c>
       <c r="AB16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC16" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="AC16" t="s" s="2">
+      <c r="AD16" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AE16" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="AD16" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AE16" t="s" s="2">
+      <c r="AF16" t="s" s="2">
         <v>76</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>38</v>
@@ -2803,10 +2745,10 @@
         <v>37</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>67</v>
+        <v>37</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>37</v>
@@ -2815,18 +2757,15 @@
         <v>37</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AO16" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2849,16 +2788,16 @@
         <v>44</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="L17" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>112</v>
-      </c>
-      <c r="M17" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>114</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -2908,7 +2847,7 @@
         <v>37</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>38</v>
@@ -2917,13 +2856,13 @@
         <v>43</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="AJ17" t="s" s="2">
         <v>62</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>117</v>
+        <v>37</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>37</v>
@@ -2932,18 +2871,15 @@
         <v>37</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AO17" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2966,23 +2902,23 @@
         <v>44</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>37</v>
       </c>
       <c r="Q18" t="s" s="2">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="R18" t="s" s="2">
         <v>37</v>
@@ -3027,7 +2963,7 @@
         <v>37</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>38</v>
@@ -3036,13 +2972,13 @@
         <v>43</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="AJ18" t="s" s="2">
         <v>62</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>124</v>
+        <v>37</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>37</v>
@@ -3051,18 +2987,15 @@
         <v>37</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AO18" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3088,10 +3021,10 @@
         <v>59</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3142,7 +3075,7 @@
         <v>37</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>43</v>
@@ -3154,7 +3087,7 @@
         <v>37</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>37</v>
@@ -3166,18 +3099,15 @@
         <v>37</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AO19" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3272,7 +3202,7 @@
         <v>37</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>67</v>
+        <v>37</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>37</v>
@@ -3281,22 +3211,19 @@
         <v>37</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AO20" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -3315,16 +3242,16 @@
         <v>37</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>70</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="M21" t="s" s="2">
         <v>71</v>
       </c>
-      <c r="M21" t="s" s="2">
+      <c r="N21" t="s" s="2">
         <v>72</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>73</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -3362,19 +3289,19 @@
         <v>37</v>
       </c>
       <c r="AB21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC21" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="AC21" t="s" s="2">
+      <c r="AD21" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AE21" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="AD21" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AE21" t="s" s="2">
+      <c r="AF21" t="s" s="2">
         <v>76</v>
-      </c>
-      <c r="AF21" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>38</v>
@@ -3386,10 +3313,10 @@
         <v>37</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>67</v>
+        <v>37</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>37</v>
@@ -3398,22 +3325,19 @@
         <v>37</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AO21" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -3432,19 +3356,19 @@
         <v>44</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="M22" t="s" s="2">
+      <c r="N22" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="O22" t="s" s="2">
         <v>82</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>37</v>
@@ -3493,7 +3417,7 @@
         <v>37</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>38</v>
@@ -3505,10 +3429,10 @@
         <v>37</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>85</v>
+        <v>37</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>37</v>
@@ -3517,18 +3441,15 @@
         <v>37</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AO22" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3551,13 +3472,13 @@
         <v>44</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3584,11 +3505,11 @@
         <v>37</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="Y23" s="2"/>
       <c r="Z23" t="s" s="2">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>37</v>
@@ -3606,7 +3527,7 @@
         <v>37</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>43</v>
@@ -3621,27 +3542,24 @@
         <v>37</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>37</v>
+        <v>134</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>138</v>
+        <v>37</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AO23" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3664,13 +3582,13 @@
         <v>44</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3721,7 +3639,7 @@
         <v>37</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>43</v>
@@ -3736,27 +3654,24 @@
         <v>37</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>37</v>
+        <v>138</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>142</v>
+        <v>37</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AO24" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3779,13 +3694,13 @@
         <v>44</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3836,7 +3751,7 @@
         <v>37</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>38</v>
@@ -3851,27 +3766,24 @@
         <v>37</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>37</v>
+        <v>142</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AO25" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3894,13 +3806,13 @@
         <v>44</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3951,7 +3863,7 @@
         <v>37</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>38</v>
@@ -3966,27 +3878,24 @@
         <v>37</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>37</v>
+        <v>146</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>150</v>
+        <v>37</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AO26" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4012,10 +3921,10 @@
         <v>45</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4066,7 +3975,7 @@
         <v>37</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>43</v>
@@ -4081,27 +3990,24 @@
         <v>37</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>37</v>
+        <v>150</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>154</v>
+        <v>37</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AO27" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4124,13 +4030,13 @@
         <v>44</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4181,7 +4087,7 @@
         <v>37</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>43</v>
@@ -4196,27 +4102,24 @@
         <v>37</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>37</v>
+        <v>154</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>158</v>
+        <v>37</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AO28" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4242,10 +4145,10 @@
         <v>49</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4296,7 +4199,7 @@
         <v>37</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>38</v>
@@ -4311,27 +4214,24 @@
         <v>37</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>37</v>
+        <v>158</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>162</v>
+        <v>37</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AO29" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4354,13 +4254,13 @@
         <v>44</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4411,42 +4311,39 @@
         <v>37</v>
       </c>
       <c r="AF30" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="AG30" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="AH30" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="AI30" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AJ30" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AK30" t="s" s="2">
         <v>163</v>
       </c>
-      <c r="AG30" t="s" s="2">
-        <v>43</v>
-      </c>
-      <c r="AH30" t="s" s="2">
-        <v>43</v>
-      </c>
-      <c r="AI30" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AJ30" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AK30" t="s" s="2">
-        <v>37</v>
-      </c>
       <c r="AL30" t="s" s="2">
-        <v>167</v>
+        <v>37</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AO30" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4469,13 +4366,13 @@
         <v>37</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4526,7 +4423,7 @@
         <v>37</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>38</v>
@@ -4541,27 +4438,24 @@
         <v>37</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>37</v>
+        <v>167</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>171</v>
+        <v>37</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AO31" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4584,13 +4478,13 @@
         <v>44</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4617,11 +4511,11 @@
         <v>37</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="Y32" s="2"/>
       <c r="Z32" t="s" s="2">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>37</v>
@@ -4639,42 +4533,39 @@
         <v>37</v>
       </c>
       <c r="AF32" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="AG32" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="AH32" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="AI32" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AJ32" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AK32" t="s" s="2">
         <v>172</v>
       </c>
-      <c r="AG32" t="s" s="2">
-        <v>43</v>
-      </c>
-      <c r="AH32" t="s" s="2">
-        <v>43</v>
-      </c>
-      <c r="AI32" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AJ32" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AK32" t="s" s="2">
-        <v>37</v>
-      </c>
       <c r="AL32" t="s" s="2">
-        <v>176</v>
+        <v>37</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AO32" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4700,10 +4591,10 @@
         <v>45</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4754,7 +4645,7 @@
         <v>37</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>38</v>
@@ -4769,27 +4660,24 @@
         <v>37</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>37</v>
+        <v>176</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>180</v>
+        <v>37</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AO33" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4812,13 +4700,13 @@
         <v>37</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4869,7 +4757,7 @@
         <v>37</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>38</v>
@@ -4895,16 +4783,13 @@
       <c r="AN34" t="s" s="2">
         <v>37</v>
       </c>
-      <c r="AO34" t="s" s="2">
-        <v>37</v>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4930,10 +4815,10 @@
         <v>54</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4984,7 +4869,7 @@
         <v>37</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>38</v>
@@ -4999,27 +4884,24 @@
         <v>37</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>37</v>
+        <v>184</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>188</v>
+        <v>37</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AO35" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5042,13 +4924,13 @@
         <v>37</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5075,11 +4957,11 @@
         <v>37</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="Y36" s="2"/>
       <c r="Z36" t="s" s="2">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>37</v>
@@ -5097,7 +4979,7 @@
         <v>37</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>38</v>
@@ -5112,27 +4994,24 @@
         <v>37</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>37</v>
+        <v>189</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>193</v>
+        <v>37</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AO36" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5158,10 +5037,10 @@
         <v>49</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5212,7 +5091,7 @@
         <v>37</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>38</v>
@@ -5230,15 +5109,12 @@
         <v>37</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>37</v>
+        <v>193</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>197</v>
+        <v>37</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AO37" t="s" s="2">
         <v>37</v>
       </c>
     </row>
